--- a/attendance_history/Absent_2026-03-28.xlsx
+++ b/attendance_history/Absent_2026-03-28.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -556,39 +556,39 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sky deal </t>
+          <t>KAYESU PHIONAH</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2024-08-16867</t>
+          <t>2023-08-18840</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>BBA</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>EVENING</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>BBA</t>
+          <t>somac</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>KAYESU PHIONAH</t>
+          <t>TUMUSIIME ALEX</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2023-08-18840</t>
+          <t>2023-08-17666</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>somac</t>
+          <t>SOMAC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TUMUSIIME ALEX</t>
+          <t>NAGUDHI MARIAM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2023-08-17666</t>
+          <t>2023-08-12345</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>BIT</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -629,33 +629,6 @@
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>SOMAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>NAGUDHI MARIAM</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>2023-08-12345</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>BIT</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>EVENING</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>SOMAC</t>
         </is>
